--- a/docs/dev/QA记录.xlsx
+++ b/docs/dev/QA记录.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,6 +617,26 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>短名解析策略：当前全局唯一，多模块下跨概念/跨数据源重名应合法</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>当前：重名报错（防静默覆盖）；P1：作用域感知解析 + 前缀消歧（ds1.Todo），允许跨概念重名</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>已记录（P1 待办）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/dev/QA记录.xlsx
+++ b/docs/dev/QA记录.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -637,6 +637,156 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M7 拆分标准：按功能纵向切（用户确认），共享数据模型独立文件，跨文件引用最少；语言层零约束，拆法是使用策略</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M7 拆分方式：import vs 全局命名空间</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>全局命名空间（对标 NASL，无 import），link 前合并</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M7 发现既有 bug：declareGlobal 以 existing!==path 判重，同名 logic path 恒等导致同段重名一直漏报</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>收紧为同 path 也报错，新增双文件报错单测</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M7 app 名带连字符（todo-multi）→ Java 包名/类名非法，此前硬编码 todo 未暴露</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>codegen-java pkgOf 入口校验合法 Java 标识符并抛错；示例改用 todomulti</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M7 对拍首跑失败：两侧 app 名不同致包名/路径全不同（非语义漂移）</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>app 名是入参非解析产物，对拍前对齐 singleApp.name</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M8 CLI 运行形态：不开构建链，bin 经 tsx ESM register 加载 TS 源（与全仓 packages main=src/index.ts 形态一致）</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M8 发现 type AppNode 从 @tdsl/parser 导入但 parser 不导出该类型，TS 静默当 any（隐式 any 报错才暴露）</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>语义核类型一律从 @tdsl/core 导入，已入库踩坑</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M8 build 端到端：dsl build examples/todo-multi/tdsl -o generated → mvn compile + vite build 通过（java 20 + react 12 files）</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>已验证</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/dev/QA记录.xlsx
+++ b/docs/dev/QA记录.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -787,6 +787,146 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dev/43 需求分析（业务动作状态化与链路联动）：F1 按钮 visible/disabled 条件绑定 + F2 详情子表与明细合计 + F3 ERP 单据库存/核销联动；CRM 仅按钮状态化</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dev/44 系统设计：parser/core 零改动（挂 props）· typecheck 小改（summary + 条件宽松）· codegen-react 主战场（条件渲染/枚举字面量/detail 子表/summary）· F3 纯 logic · F2 样例落 2 单据（采购入库/销售出库）</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dev/45 详细设计：enumMemberLiteralOf/可见性条件/disabled/summary 归约/detail 子表列复用 columnDefsOf；typecheck SUMMARY-TARGET·EXPR；yudao applyStock+联动+2 详情聚合结构体+按钮条件+seed 调整；测试矩阵 T1-T6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>dev/45 阶段五真机：A1-A6 全通过（库存140/流水/订单inCount=70自动AUDITED/库存不足回滚/详情聚合/核销回写93261与48920）；seed 104-0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dev/45 阶段六交付：语法手册§4 补齐 visible·disabled·summary·detail子表；交付形态适配（语言面文档替代 docs/api+Postman）</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>用户实测追加：右上角动作区 + 标题分隔线 + 详情抽屉 + 抽屉标题按模式 + 行内链接按钮 + 删除二次确认</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>用户实测缺陷：列表无分页（genTable 硬编码 pagination=false）→ 客户端分页；连带根因 rowKey 取首列字段重复（库存明细 productId）导致翻页残留旧行 → 改用实体主键</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/dev/QA记录.xlsx
+++ b/docs/dev/QA记录.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -927,6 +927,126 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>dev/46 需求分析（ERP 门户看板与角色视角）：F1 看板组件（statistic 绑查询 / row·col 栅格 / carousel / list）；F2 聚合查询 react 端贯通；F3 @role 注解 + 角色切换器（演示级）；F4 yudao 5 个门户样例</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>待用户 Gate</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dev/47 系统设计：parser 极小改（@role）；typecheck 组件白名单；codegen-react 组件映射(Grid/Carousel/List)+statistic 标量+角色过滤与切换器；java 零改动；groupBy 列表渲染本轮不做</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>待用户 Gate</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>dev/48 详细设计：范围修正新增 F2b（C1 补齐 where+aggregate，实测确认为收敛改动：java 聚合分支补 WHERE + typecheck 链放宽，react 零改动）；@role 4 行；组件映射/statistic/角色切换器落点；yudao 9 统计 logic + 5 门户 + check-spec kind:dashboard</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>待用户 Gate</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>29</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>dev/48 门户看板：C1 补齐（where(...).aggregate）→ 16 个 /api/portal/stats/* 真机 200；门户接口 404 排查=后端未重启（非代码缺陷）</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>30</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>门户样式三轮：指标卡配色/大数字、轮播渐变 Banner、列表 Meta+分页、栅格等高；缺陷修复=列表枚举裸名(UNFOLLOWED→中文 Tag)+JSX 文案 &lt; 截断(jsxText 转义)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>31</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>角色视角：@role 语法保留但外壳去掉切换/过滤（用户拍板）；门户文件 05-portal 置顶菜单，首页=第一个列表页</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/dev/QA记录.xlsx
+++ b/docs/dev/QA记录.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1047,6 +1047,106 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M11 鉴权：FFI_CORE 五域守门测试撞 Auth 域</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>按新口径更新：五语言域 + 平台鉴权域（无 maven 坐标，internal 标记 import 跳过）</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M11 块注释 /* */ 不被 lexer 支持（yudao 70-auth.tdsl 样例报 unexpected char）</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>确认边界：lexer 仅 //；样例改行注释；块注释支持列为独立余项</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M11 语言边界：无一元 !（手册漂移）；List.get(0) 字段访问 java 无类型通道</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>样例用 for-of 与 === false 规避；语法手册 §2 漂移已修；get(0) 通道留 M3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M11 react：公开页 Space 多收致 TS6133 / register 成功链 d 未用 / RequireAuth 包装正则</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>collectAntdComponents 按 @public 排除动作区组件；successChain 按是否用返回值选形；改为构造期包装</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M11 register 接口返回实体会带出密码哈希</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>演示口径可接受；商用需投影脱敏（记录为余项）</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>保持观察</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
